--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig7_daily_timeseries_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig7_daily_timeseries_data.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -577,7 +577,7 @@
         <v>4.559858583569047</v>
       </c>
       <c r="I2" t="n">
-        <v>4.153156272708621</v>
+        <v>4.151416525342037</v>
       </c>
       <c r="J2" t="n">
         <v>4.633478975630743</v>
@@ -624,7 +624,7 @@
         <v>4.559811912563653</v>
       </c>
       <c r="I3" t="n">
-        <v>4.108471672261055</v>
+        <v>4.121199991956036</v>
       </c>
       <c r="J3" t="n">
         <v>4.563029565319777</v>
@@ -671,7 +671,7 @@
         <v>4.558145200168714</v>
       </c>
       <c r="I4" t="n">
-        <v>4.135910572495746</v>
+        <v>4.137822884128885</v>
       </c>
       <c r="J4" t="n">
         <v>4.520621306748454</v>
@@ -718,7 +718,7 @@
         <v>4.689040677126343</v>
       </c>
       <c r="I5" t="n">
-        <v>4.069689060033626</v>
+        <v>4.088116151578912</v>
       </c>
       <c r="J5" t="n">
         <v>4.499666930587749</v>
@@ -765,7 +765,7 @@
         <v>4.37713341586965</v>
       </c>
       <c r="I6" t="n">
-        <v>4.067527332767188</v>
+        <v>4.09571019189473</v>
       </c>
       <c r="J6" t="n">
         <v>4.539421178433606</v>
@@ -812,7 +812,7 @@
         <v>4.173143801860332</v>
       </c>
       <c r="I7" t="n">
-        <v>4.082499748378314</v>
+        <v>4.089917489568961</v>
       </c>
       <c r="J7" t="n">
         <v>4.431030099066233</v>
@@ -859,7 +859,7 @@
         <v>4.797298545616593</v>
       </c>
       <c r="I8" t="n">
-        <v>4.134514664799293</v>
+        <v>4.121590571837936</v>
       </c>
       <c r="J8" t="n">
         <v>4.512057481724544</v>
@@ -906,7 +906,7 @@
         <v>4.499989257739241</v>
       </c>
       <c r="I9" t="n">
-        <v>4.050826941923483</v>
+        <v>4.036389125570178</v>
       </c>
       <c r="J9" t="n">
         <v>4.530622956232982</v>
@@ -953,7 +953,7 @@
         <v>4.679344895350202</v>
       </c>
       <c r="I10" t="n">
-        <v>4.097113015248592</v>
+        <v>4.093444644983446</v>
       </c>
       <c r="J10" t="n">
         <v>4.472796007273075</v>
@@ -1000,7 +1000,7 @@
         <v>4.762066548574987</v>
       </c>
       <c r="I11" t="n">
-        <v>4.081741274789655</v>
+        <v>4.088439583843536</v>
       </c>
       <c r="J11" t="n">
         <v>4.399766657862697</v>
@@ -1047,7 +1047,7 @@
         <v>4.599359769984783</v>
       </c>
       <c r="I12" t="n">
-        <v>4.44332567141042</v>
+        <v>4.449464704341334</v>
       </c>
       <c r="J12" t="n">
         <v>4.504213538616297</v>
@@ -1094,7 +1094,7 @@
         <v>4.571752214425884</v>
       </c>
       <c r="I13" t="n">
-        <v>4.149233706451636</v>
+        <v>4.156748236213803</v>
       </c>
       <c r="J13" t="n">
         <v>4.458842608794253</v>
@@ -1141,7 +1141,7 @@
         <v>4.411922325751128</v>
       </c>
       <c r="I14" t="n">
-        <v>4.414656035284396</v>
+        <v>4.405829330719047</v>
       </c>
       <c r="J14" t="n">
         <v>4.471585999119213</v>
@@ -1188,7 +1188,7 @@
         <v>4.287302105686356</v>
       </c>
       <c r="I15" t="n">
-        <v>4.024353042492776</v>
+        <v>4.018086590385874</v>
       </c>
       <c r="J15" t="n">
         <v>4.46431431959523</v>
@@ -1235,7 +1235,7 @@
         <v>4.486766475549089</v>
       </c>
       <c r="I16" t="n">
-        <v>4.372605952291516</v>
+        <v>4.370003207346478</v>
       </c>
       <c r="J16" t="n">
         <v>4.497464595766229</v>
@@ -1282,7 +1282,7 @@
         <v>4.715041131569031</v>
       </c>
       <c r="I17" t="n">
-        <v>4.07264400903921</v>
+        <v>4.076151039098381</v>
       </c>
       <c r="J17" t="n">
         <v>4.532588952241186</v>
@@ -1329,7 +1329,7 @@
         <v>4.521048502404039</v>
       </c>
       <c r="I18" t="n">
-        <v>4.076968914003615</v>
+        <v>4.072117183602623</v>
       </c>
       <c r="J18" t="n">
         <v>4.624554930761033</v>
@@ -1376,7 +1376,7 @@
         <v>4.512070949703448</v>
       </c>
       <c r="I19" t="n">
-        <v>3.934332551757466</v>
+        <v>3.912851760044832</v>
       </c>
       <c r="J19" t="n">
         <v>4.477676227742597</v>
@@ -1423,7 +1423,7 @@
         <v>4.530345467936095</v>
       </c>
       <c r="I20" t="n">
-        <v>4.080447409763337</v>
+        <v>4.084426006715913</v>
       </c>
       <c r="J20" t="n">
         <v>4.434762468538774</v>
@@ -1470,7 +1470,7 @@
         <v>4.484786975704517</v>
       </c>
       <c r="I21" t="n">
-        <v>4.062666266122918</v>
+        <v>4.053297890643492</v>
       </c>
       <c r="J21" t="n">
         <v>4.411668107392295</v>
@@ -1517,7 +1517,7 @@
         <v>4.543394045144982</v>
       </c>
       <c r="I22" t="n">
-        <v>4.41181902681603</v>
+        <v>4.435406659452992</v>
       </c>
       <c r="J22" t="n">
         <v>4.492413137054577</v>
@@ -1564,7 +1564,7 @@
         <v>4.829658664998105</v>
       </c>
       <c r="I23" t="n">
-        <v>4.097281539871509</v>
+        <v>4.093952586746775</v>
       </c>
       <c r="J23" t="n">
         <v>4.422131849408522</v>
@@ -1611,7 +1611,7 @@
         <v>4.503566696322391</v>
       </c>
       <c r="I24" t="n">
-        <v>4.433072903022138</v>
+        <v>4.416644471476268</v>
       </c>
       <c r="J24" t="n">
         <v>4.479101553781644</v>
@@ -1658,7 +1658,7 @@
         <v>4.638632599056677</v>
       </c>
       <c r="I25" t="n">
-        <v>4.105538731885394</v>
+        <v>4.102072429100232</v>
       </c>
       <c r="J25" t="n">
         <v>4.415937253952781</v>
@@ -1705,7 +1705,7 @@
         <v>4.83549084852825</v>
       </c>
       <c r="I26" t="n">
-        <v>4.315894651757569</v>
+        <v>4.330989531511189</v>
       </c>
       <c r="J26" t="n">
         <v>4.508924659855547</v>
@@ -1752,7 +1752,7 @@
         <v>4.714423630267505</v>
       </c>
       <c r="I27" t="n">
-        <v>4.024194449391857</v>
+        <v>4.021327924920511</v>
       </c>
       <c r="J27" t="n">
         <v>4.491545497961882</v>
@@ -1799,7 +1799,7 @@
         <v>4.531431368368642</v>
       </c>
       <c r="I28" t="n">
-        <v>3.685876182395067</v>
+        <v>3.681079496317796</v>
       </c>
       <c r="J28" t="n">
         <v>4.481083738359398</v>
@@ -1846,7 +1846,7 @@
         <v>4.528435978604099</v>
       </c>
       <c r="I29" t="n">
-        <v>4.088689909668284</v>
+        <v>4.088913613509249</v>
       </c>
       <c r="J29" t="n">
         <v>4.428957388525998</v>
@@ -1893,7 +1893,7 @@
         <v>4.836722576333989</v>
       </c>
       <c r="I30" t="n">
-        <v>4.086870156356115</v>
+        <v>4.086673657311445</v>
       </c>
       <c r="J30" t="n">
         <v>4.431452624616089</v>
@@ -1940,7 +1940,7 @@
         <v>4.528200091584026</v>
       </c>
       <c r="I31" t="n">
-        <v>4.083504197583384</v>
+        <v>4.081133677226444</v>
       </c>
       <c r="J31" t="n">
         <v>4.404890672709293</v>
@@ -1987,7 +1987,7 @@
         <v>4.846610369842201</v>
       </c>
       <c r="I32" t="n">
-        <v>4.046717032369797</v>
+        <v>4.038364740439009</v>
       </c>
       <c r="J32" t="n">
         <v>4.437075911745612</v>
@@ -2034,7 +2034,7 @@
         <v>4.815148255076682</v>
       </c>
       <c r="I33" t="n">
-        <v>4.032649567302867</v>
+        <v>4.029494118495673</v>
       </c>
       <c r="J33" t="n">
         <v>4.4047524034143</v>
@@ -2081,7 +2081,7 @@
         <v>4.830331169231258</v>
       </c>
       <c r="I34" t="n">
-        <v>4.05671253786458</v>
+        <v>4.063641458596617</v>
       </c>
       <c r="J34" t="n">
         <v>4.492970197648399</v>
@@ -2128,7 +2128,7 @@
         <v>4.804257244361244</v>
       </c>
       <c r="I35" t="n">
-        <v>3.983516530201013</v>
+        <v>3.981899284963968</v>
       </c>
       <c r="J35" t="n">
         <v>4.430754119168774</v>
@@ -2175,7 +2175,7 @@
         <v>4.52229455432204</v>
       </c>
       <c r="I36" t="n">
-        <v>4.251545650986005</v>
+        <v>4.251466078881236</v>
       </c>
       <c r="J36" t="n">
         <v>4.474531498814111</v>
@@ -2222,7 +2222,7 @@
         <v>4.513736060043716</v>
       </c>
       <c r="I37" t="n">
-        <v>4.070182393494996</v>
+        <v>4.068442442357467</v>
       </c>
       <c r="J37" t="n">
         <v>4.486996365856541</v>
@@ -2269,7 +2269,7 @@
         <v>4.527132511544448</v>
       </c>
       <c r="I38" t="n">
-        <v>4.374351287498043</v>
+        <v>4.376238670222184</v>
       </c>
       <c r="J38" t="n">
         <v>4.444849695382301</v>
@@ -2316,7 +2316,7 @@
         <v>4.458142661970922</v>
       </c>
       <c r="I39" t="n">
-        <v>3.954520161777645</v>
+        <v>3.95394866488352</v>
       </c>
       <c r="J39" t="n">
         <v>4.379244834255371</v>
@@ -2363,7 +2363,7 @@
         <v>4.668227942448699</v>
       </c>
       <c r="I40" t="n">
-        <v>4.073669134949177</v>
+        <v>4.072273771177337</v>
       </c>
       <c r="J40" t="n">
         <v>4.440659861400857</v>
@@ -2410,7 +2410,7 @@
         <v>4.188084252335081</v>
       </c>
       <c r="I41" t="n">
-        <v>3.654215322302795</v>
+        <v>3.652627660616231</v>
       </c>
       <c r="J41" t="n">
         <v>4.442812062880172</v>
@@ -2457,7 +2457,7 @@
         <v>4.48747291046022</v>
       </c>
       <c r="I42" t="n">
-        <v>3.548212853244613</v>
+        <v>3.743774351667039</v>
       </c>
       <c r="J42" t="n">
         <v>4.380364213967535</v>
@@ -2504,7 +2504,7 @@
         <v>4.497714321110672</v>
       </c>
       <c r="I43" t="n">
-        <v>3.730304620916012</v>
+        <v>3.740800444833041</v>
       </c>
       <c r="J43" t="n">
         <v>4.416499945576501</v>
@@ -2551,7 +2551,7 @@
         <v>3.920233105464475</v>
       </c>
       <c r="I44" t="n">
-        <v>3.913969831932504</v>
+        <v>3.891455125146871</v>
       </c>
       <c r="J44" t="n">
         <v>4.296175711843087</v>
@@ -2598,7 +2598,7 @@
         <v>3.78899216178006</v>
       </c>
       <c r="I45" t="n">
-        <v>3.564102638628194</v>
+        <v>3.77233506225895</v>
       </c>
       <c r="J45" t="n">
         <v>4.319161406631799</v>
@@ -2645,7 +2645,7 @@
         <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>4.030648792961951</v>
+        <v>4.045804887716488</v>
       </c>
       <c r="J46" t="n">
         <v>4.420029555790808</v>
@@ -2692,7 +2692,7 @@
         <v>2.5</v>
       </c>
       <c r="I47" t="n">
-        <v>4.045542388426125</v>
+        <v>4.265144103009572</v>
       </c>
       <c r="J47" t="n">
         <v>4.306107624521115</v>
@@ -2739,7 +2739,7 @@
         <v>2.5</v>
       </c>
       <c r="I48" t="n">
-        <v>4.487123144226888</v>
+        <v>4.476774203442916</v>
       </c>
       <c r="J48" t="n">
         <v>4.410746952868738</v>
@@ -2786,7 +2786,7 @@
         <v>2.5</v>
       </c>
       <c r="I49" t="n">
-        <v>3.678078082737235</v>
+        <v>3.683920596561672</v>
       </c>
       <c r="J49" t="n">
         <v>4.22917724137014</v>
@@ -2833,7 +2833,7 @@
         <v>2.5</v>
       </c>
       <c r="I50" t="n">
-        <v>3.19738849611897</v>
+        <v>3.471221525649382</v>
       </c>
       <c r="J50" t="n">
         <v>4.378356239512506</v>
@@ -2880,7 +2880,7 @@
         <v>2.5</v>
       </c>
       <c r="I51" t="n">
-        <v>2.977234820821886</v>
+        <v>3.029137015654581</v>
       </c>
       <c r="J51" t="n">
         <v>4.456619120865858</v>
@@ -2927,7 +2927,7 @@
         <v>2.5</v>
       </c>
       <c r="I52" t="n">
-        <v>2.991948938079037</v>
+        <v>3.023452900212603</v>
       </c>
       <c r="J52" t="n">
         <v>3.463638134532656</v>
@@ -2974,7 +2974,7 @@
         <v>2.5</v>
       </c>
       <c r="I53" t="n">
-        <v>3.38185711404578</v>
+        <v>3.669931042060452</v>
       </c>
       <c r="J53" t="n">
         <v>3.887234977569297</v>
@@ -3021,7 +3021,7 @@
         <v>2.5</v>
       </c>
       <c r="I54" t="n">
-        <v>3.841695904412244</v>
+        <v>3.887765096127104</v>
       </c>
       <c r="J54" t="n">
         <v>4.357996829155575</v>
@@ -3068,7 +3068,7 @@
         <v>2.5</v>
       </c>
       <c r="I55" t="n">
-        <v>4.027156332762059</v>
+        <v>4.0748856568637</v>
       </c>
       <c r="J55" t="n">
         <v>4.391312453688103</v>
@@ -3115,7 +3115,7 @@
         <v>2.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4.1668057557503</v>
+        <v>4.163112867469493</v>
       </c>
       <c r="J56" t="n">
         <v>4.491730740138231</v>
@@ -3162,7 +3162,7 @@
         <v>2.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4.237978161932609</v>
+        <v>4.246769101729025</v>
       </c>
       <c r="J57" t="n">
         <v>4.462629337857776</v>
@@ -3209,7 +3209,7 @@
         <v>2.5</v>
       </c>
       <c r="I58" t="n">
-        <v>4.170805321200435</v>
+        <v>4.329682890930207</v>
       </c>
       <c r="J58" t="n">
         <v>4.367087239571817</v>
@@ -3256,7 +3256,7 @@
         <v>2.5</v>
       </c>
       <c r="I59" t="n">
-        <v>3.844024996309766</v>
+        <v>4.016823545745504</v>
       </c>
       <c r="J59" t="n">
         <v>4.314466105125359</v>
@@ -3303,7 +3303,7 @@
         <v>2.5</v>
       </c>
       <c r="I60" t="n">
-        <v>4.39768285208026</v>
+        <v>4.433191251526726</v>
       </c>
       <c r="J60" t="n">
         <v>4.407741788681326</v>
@@ -3350,7 +3350,7 @@
         <v>2.5</v>
       </c>
       <c r="I61" t="n">
-        <v>4.261149745830941</v>
+        <v>4.416135325135981</v>
       </c>
       <c r="J61" t="n">
         <v>4.446295030293048</v>
@@ -3397,7 +3397,7 @@
         <v>2.5</v>
       </c>
       <c r="I62" t="n">
-        <v>4.297458237035225</v>
+        <v>4.387681204251529</v>
       </c>
       <c r="J62" t="n">
         <v>4.358261360968985</v>
@@ -3444,7 +3444,7 @@
         <v>2.5</v>
       </c>
       <c r="I63" t="n">
-        <v>3.826926770509385</v>
+        <v>3.980373137567584</v>
       </c>
       <c r="J63" t="n">
         <v>4.450120979064915</v>
@@ -3491,7 +3491,7 @@
         <v>2.5</v>
       </c>
       <c r="I64" t="n">
-        <v>4.147083473207697</v>
+        <v>4.256514373651891</v>
       </c>
       <c r="J64" t="n">
         <v>4.315398634581579</v>
@@ -3538,7 +3538,7 @@
         <v>2.5</v>
       </c>
       <c r="I65" t="n">
-        <v>4.384596494012298</v>
+        <v>4.432462686026913</v>
       </c>
       <c r="J65" t="n">
         <v>4.422170319722673</v>
@@ -3585,7 +3585,7 @@
         <v>2.5</v>
       </c>
       <c r="I66" t="n">
-        <v>4.234519349828018</v>
+        <v>4.312460638318703</v>
       </c>
       <c r="J66" t="n">
         <v>4.495804676155532</v>
@@ -3632,7 +3632,7 @@
         <v>2.5</v>
       </c>
       <c r="I67" t="n">
-        <v>4.413848000561416</v>
+        <v>4.452865149952767</v>
       </c>
       <c r="J67" t="n">
         <v>4.409851541174767</v>
@@ -3679,7 +3679,7 @@
         <v>2.5</v>
       </c>
       <c r="I68" t="n">
-        <v>3.900283710383607</v>
+        <v>4.219326433056073</v>
       </c>
       <c r="J68" t="n">
         <v>4.252628141948342</v>
@@ -3726,7 +3726,7 @@
         <v>2.5</v>
       </c>
       <c r="I69" t="n">
-        <v>3.726307787045203</v>
+        <v>3.826383612866252</v>
       </c>
       <c r="J69" t="n">
         <v>4.327281580410832</v>
@@ -3773,7 +3773,7 @@
         <v>2.5</v>
       </c>
       <c r="I70" t="n">
-        <v>4.181280922020091</v>
+        <v>4.281611296528676</v>
       </c>
       <c r="J70" t="n">
         <v>4.091331342736821</v>
@@ -3820,7 +3820,7 @@
         <v>4.573650357795712</v>
       </c>
       <c r="I71" t="n">
-        <v>4.401658962870348</v>
+        <v>4.384250098324941</v>
       </c>
       <c r="J71" t="n">
         <v>4.313925991197772</v>
@@ -3867,7 +3867,7 @@
         <v>4.489422109493624</v>
       </c>
       <c r="I72" t="n">
-        <v>4.416438982456816</v>
+        <v>4.376973542848152</v>
       </c>
       <c r="J72" t="n">
         <v>4.400982482454041</v>
@@ -3914,7 +3914,7 @@
         <v>4.435163901804063</v>
       </c>
       <c r="I73" t="n">
-        <v>3.999105892585586</v>
+        <v>3.977048680152246</v>
       </c>
       <c r="J73" t="n">
         <v>4.279041719968473</v>
@@ -3961,7 +3961,7 @@
         <v>4.742227539982574</v>
       </c>
       <c r="I74" t="n">
-        <v>4.000870412298626</v>
+        <v>4.002101067769051</v>
       </c>
       <c r="J74" t="n">
         <v>4.367587782026453</v>
@@ -4008,7 +4008,7 @@
         <v>3.977240984638448</v>
       </c>
       <c r="I75" t="n">
-        <v>4.007425301870081</v>
+        <v>4.01116287811441</v>
       </c>
       <c r="J75" t="n">
         <v>4.384348277122641</v>
@@ -4055,7 +4055,7 @@
         <v>4.199816465971631</v>
       </c>
       <c r="I76" t="n">
-        <v>4.127795153174869</v>
+        <v>4.12351037797044</v>
       </c>
       <c r="J76" t="n">
         <v>4.385489462979096</v>
@@ -4102,7 +4102,7 @@
         <v>4.333606595953164</v>
       </c>
       <c r="I77" t="n">
-        <v>4.108118111632813</v>
+        <v>4.092167602359291</v>
       </c>
       <c r="J77" t="n">
         <v>4.21387955503002</v>
@@ -4149,7 +4149,7 @@
         <v>4.445291661423149</v>
       </c>
       <c r="I78" t="n">
-        <v>4.419904961822982</v>
+        <v>4.422842736729353</v>
       </c>
       <c r="J78" t="n">
         <v>4.349222410216742</v>
@@ -4196,7 +4196,7 @@
         <v>4.425259794487646</v>
       </c>
       <c r="I79" t="n">
-        <v>3.985949713214941</v>
+        <v>3.984496502584216</v>
       </c>
       <c r="J79" t="n">
         <v>4.346398400781576</v>
@@ -4243,7 +4243,7 @@
         <v>4.519722609000282</v>
       </c>
       <c r="I80" t="n">
-        <v>4.082044648146669</v>
+        <v>4.085349753169094</v>
       </c>
       <c r="J80" t="n">
         <v>4.370782869521932</v>
@@ -4290,7 +4290,7 @@
         <v>3.393645064868232</v>
       </c>
       <c r="I81" t="n">
-        <v>3.970522360932867</v>
+        <v>4.031148170592644</v>
       </c>
       <c r="J81" t="n">
         <v>3.596858629275493</v>
@@ -4337,7 +4337,7 @@
         <v>3.433618947129155</v>
       </c>
       <c r="I82" t="n">
-        <v>4.019980934740573</v>
+        <v>4.059076575820821</v>
       </c>
       <c r="J82" t="n">
         <v>4.022556108520424</v>
@@ -4384,7 +4384,7 @@
         <v>3.88257835047632</v>
       </c>
       <c r="I83" t="n">
-        <v>3.785671934907363</v>
+        <v>3.838542269353629</v>
       </c>
       <c r="J83" t="n">
         <v>3.664642838023817</v>
@@ -4431,7 +4431,7 @@
         <v>4.016946038609127</v>
       </c>
       <c r="I84" t="n">
-        <v>2.962641698742997</v>
+        <v>3.174379445636694</v>
       </c>
       <c r="J84" t="n">
         <v>3.933558159559963</v>
@@ -4478,7 +4478,7 @@
         <v>4.166911887832171</v>
       </c>
       <c r="I85" t="n">
-        <v>4.023143649579564</v>
+        <v>4.05071024837761</v>
       </c>
       <c r="J85" t="n">
         <v>4.3575781190103</v>
@@ -4525,7 +4525,7 @@
         <v>4.349508656216626</v>
       </c>
       <c r="I86" t="n">
-        <v>3.776302113821266</v>
+        <v>3.990205040862643</v>
       </c>
       <c r="J86" t="n">
         <v>4.368008337277089</v>
@@ -4572,7 +4572,7 @@
         <v>4.407177683782519</v>
       </c>
       <c r="I87" t="n">
-        <v>4.033893376845453</v>
+        <v>4.066238367703118</v>
       </c>
       <c r="J87" t="n">
         <v>4.178323524731318</v>
@@ -4619,7 +4619,7 @@
         <v>4.484842749406554</v>
       </c>
       <c r="I88" t="n">
-        <v>4.032976281788864</v>
+        <v>4.010362192357691</v>
       </c>
       <c r="J88" t="n">
         <v>4.079718700719194</v>
@@ -4666,7 +4666,7 @@
         <v>4.518207958414878</v>
       </c>
       <c r="I89" t="n">
-        <v>3.957969022803983</v>
+        <v>3.994229451491274</v>
       </c>
       <c r="J89" t="n">
         <v>4.205494301760163</v>
@@ -4713,7 +4713,7 @@
         <v>4.732027542830121</v>
       </c>
       <c r="I90" t="n">
-        <v>3.986249669803714</v>
+        <v>4.020539812498923</v>
       </c>
       <c r="J90" t="n">
         <v>4.483038074066983</v>
@@ -4760,7 +4760,7 @@
         <v>4.300512632345324</v>
       </c>
       <c r="I91" t="n">
-        <v>3.919709450232097</v>
+        <v>3.92859682792262</v>
       </c>
       <c r="J91" t="n">
         <v>4.368979813041765</v>
@@ -4807,7 +4807,7 @@
         <v>4.430463584600548</v>
       </c>
       <c r="I92" t="n">
-        <v>3.936633661336497</v>
+        <v>3.963875315175952</v>
       </c>
       <c r="J92" t="n">
         <v>4.264651323630906</v>
@@ -4854,7 +4854,7 @@
         <v>4.2805322892774</v>
       </c>
       <c r="I93" t="n">
-        <v>4.024227608327529</v>
+        <v>4.018642217110028</v>
       </c>
       <c r="J93" t="n">
         <v>4.332790166420825</v>
@@ -4901,7 +4901,7 @@
         <v>4.703350063955619</v>
       </c>
       <c r="I94" t="n">
-        <v>4.007396958661175</v>
+        <v>4.0201954359165</v>
       </c>
       <c r="J94" t="n">
         <v>4.114685271291558</v>
@@ -4948,7 +4948,7 @@
         <v>4.418688102413428</v>
       </c>
       <c r="I95" t="n">
-        <v>4.054526143850513</v>
+        <v>4.076051623198792</v>
       </c>
       <c r="J95" t="n">
         <v>4.16687140719335</v>
@@ -4995,7 +4995,7 @@
         <v>4.492598089464485</v>
       </c>
       <c r="I96" t="n">
-        <v>4.082370361297965</v>
+        <v>4.101331963492972</v>
       </c>
       <c r="J96" t="n">
         <v>4.291773327291631</v>
@@ -5042,7 +5042,7 @@
         <v>4.464630572496461</v>
       </c>
       <c r="I97" t="n">
-        <v>4.380976605004465</v>
+        <v>4.445504739307337</v>
       </c>
       <c r="J97" t="n">
         <v>4.165127232709255</v>
@@ -5089,7 +5089,7 @@
         <v>4.570845730045928</v>
       </c>
       <c r="I98" t="n">
-        <v>4.066077554606903</v>
+        <v>4.066830903042255</v>
       </c>
       <c r="J98" t="n">
         <v>4.313400160296553</v>
@@ -5136,7 +5136,7 @@
         <v>4.110566636408956</v>
       </c>
       <c r="I99" t="n">
-        <v>4.113277830213111</v>
+        <v>4.328407302378952</v>
       </c>
       <c r="J99" t="n">
         <v>4.342626321303103</v>
@@ -5183,7 +5183,7 @@
         <v>4.49197643924504</v>
       </c>
       <c r="I100" t="n">
-        <v>4.420346690131693</v>
+        <v>4.43926540342183</v>
       </c>
       <c r="J100" t="n">
         <v>4.312420492615617</v>
@@ -5230,7 +5230,7 @@
         <v>4.627686228210893</v>
       </c>
       <c r="I101" t="n">
-        <v>4.459920104379029</v>
+        <v>4.467508703509721</v>
       </c>
       <c r="J101" t="n">
         <v>4.406387178535478</v>
@@ -5277,7 +5277,7 @@
         <v>4.509141124368186</v>
       </c>
       <c r="I102" t="n">
-        <v>4.111885221999449</v>
+        <v>4.108061218765744</v>
       </c>
       <c r="J102" t="n">
         <v>4.384773372298078</v>
@@ -5324,7 +5324,7 @@
         <v>4.495348580771626</v>
       </c>
       <c r="I103" t="n">
-        <v>4.116896239508121</v>
+        <v>4.121207709860891</v>
       </c>
       <c r="J103" t="n">
         <v>4.354378498178998</v>
@@ -5371,7 +5371,7 @@
         <v>4.125767363354226</v>
       </c>
       <c r="I104" t="n">
-        <v>4.344033969177395</v>
+        <v>4.385337234047629</v>
       </c>
       <c r="J104" t="n">
         <v>3.933298111507122</v>
@@ -5418,7 +5418,7 @@
         <v>4.600991208290006</v>
       </c>
       <c r="I105" t="n">
-        <v>3.864333329000994</v>
+        <v>3.88676879674256</v>
       </c>
       <c r="J105" t="n">
         <v>3.432433063183836</v>
@@ -5465,7 +5465,7 @@
         <v>4.446842837788596</v>
       </c>
       <c r="I106" t="n">
-        <v>4.004730828713107</v>
+        <v>4.005749520750284</v>
       </c>
       <c r="J106" t="n">
         <v>4.147616757189088</v>
@@ -5512,7 +5512,7 @@
         <v>4.477305490391654</v>
       </c>
       <c r="I107" t="n">
-        <v>4.098278335278946</v>
+        <v>4.10004905896055</v>
       </c>
       <c r="J107" t="n">
         <v>4.212842427892182</v>
@@ -5559,7 +5559,7 @@
         <v>4.468845097545541</v>
       </c>
       <c r="I108" t="n">
-        <v>4.131789849574551</v>
+        <v>4.130317550559775</v>
       </c>
       <c r="J108" t="n">
         <v>4.302199664113665</v>
@@ -5606,7 +5606,7 @@
         <v>4.694999951547631</v>
       </c>
       <c r="I109" t="n">
-        <v>4.090908892471361</v>
+        <v>4.089643940681576</v>
       </c>
       <c r="J109" t="n">
         <v>4.418861720604098</v>
@@ -5653,7 +5653,7 @@
         <v>4.485536534964105</v>
       </c>
       <c r="I110" t="n">
-        <v>4.094334336998939</v>
+        <v>4.096817343855152</v>
       </c>
       <c r="J110" t="n">
         <v>4.396269584016249</v>
@@ -5700,7 +5700,7 @@
         <v>4.66046375583783</v>
       </c>
       <c r="I111" t="n">
-        <v>4.103375135746212</v>
+        <v>4.10711683909664</v>
       </c>
       <c r="J111" t="n">
         <v>4.370403514842957</v>
@@ -5747,7 +5747,7 @@
         <v>4.582736646949741</v>
       </c>
       <c r="I112" t="n">
-        <v>4.448589400027061</v>
+        <v>4.462956238713519</v>
       </c>
       <c r="J112" t="n">
         <v>4.069847968091816</v>
@@ -5794,7 +5794,7 @@
         <v>4.621954457278017</v>
       </c>
       <c r="I113" t="n">
-        <v>4.469114268357353</v>
+        <v>4.472999672691587</v>
       </c>
       <c r="J113" t="n">
         <v>4.406880553353721</v>
@@ -5841,7 +5841,7 @@
         <v>4.341618922573484</v>
       </c>
       <c r="I114" t="n">
-        <v>4.044258542868718</v>
+        <v>4.087476921273335</v>
       </c>
       <c r="J114" t="n">
         <v>4.353483271238535</v>
@@ -5888,7 +5888,7 @@
         <v>4.411066705360842</v>
       </c>
       <c r="I115" t="n">
-        <v>3.052875577959453</v>
+        <v>3.122152594825393</v>
       </c>
       <c r="J115" t="n">
         <v>4.356812005064457</v>
@@ -5935,7 +5935,7 @@
         <v>4.319355830918867</v>
       </c>
       <c r="I116" t="n">
-        <v>2.955807169170899</v>
+        <v>2.955805462709034</v>
       </c>
       <c r="J116" t="n">
         <v>4.376461116679478</v>
@@ -6076,7 +6076,7 @@
         <v>4.703130358767154</v>
       </c>
       <c r="I119" t="n">
-        <v>4.120849229105966</v>
+        <v>4.12375490785043</v>
       </c>
       <c r="J119" t="n">
         <v>4.3253659659104</v>
@@ -6123,7 +6123,7 @@
         <v>4.601907591698755</v>
       </c>
       <c r="I120" t="n">
-        <v>4.096032573311702</v>
+        <v>4.104823678491298</v>
       </c>
       <c r="J120" t="n">
         <v>4.393493310006013</v>
@@ -6170,7 +6170,7 @@
         <v>4.227115839575847</v>
       </c>
       <c r="I121" t="n">
-        <v>4.102680298642323</v>
+        <v>4.187927692986197</v>
       </c>
       <c r="J121" t="n">
         <v>4.259704926595633</v>
@@ -6217,7 +6217,7 @@
         <v>4.461778352268744</v>
       </c>
       <c r="I122" t="n">
-        <v>4.126432324827034</v>
+        <v>4.140196549485191</v>
       </c>
       <c r="J122" t="n">
         <v>4.345050873889482</v>
@@ -6264,7 +6264,7 @@
         <v>4.278103400979065</v>
       </c>
       <c r="I123" t="n">
-        <v>3.970341781612391</v>
+        <v>3.971882565185203</v>
       </c>
       <c r="J123" t="n">
         <v>4.344536440382613</v>
@@ -6311,7 +6311,7 @@
         <v>4.378257580593317</v>
       </c>
       <c r="I124" t="n">
-        <v>3.943653481517553</v>
+        <v>3.964081510649597</v>
       </c>
       <c r="J124" t="n">
         <v>4.413634637670225</v>
@@ -6358,7 +6358,7 @@
         <v>4.456642673334374</v>
       </c>
       <c r="I125" t="n">
-        <v>4.05995585000275</v>
+        <v>4.061728683911923</v>
       </c>
       <c r="J125" t="n">
         <v>4.391749674247243</v>
@@ -6405,7 +6405,7 @@
         <v>4.423555556784442</v>
       </c>
       <c r="I126" t="n">
-        <v>3.978950323110631</v>
+        <v>3.982848406302084</v>
       </c>
       <c r="J126" t="n">
         <v>4.431387757636205</v>
@@ -6452,7 +6452,7 @@
         <v>4.508849473748776</v>
       </c>
       <c r="I127" t="n">
-        <v>3.965493720474729</v>
+        <v>3.976620030099598</v>
       </c>
       <c r="J127" t="n">
         <v>4.416727897843767</v>
@@ -6499,7 +6499,7 @@
         <v>4.700297928165861</v>
       </c>
       <c r="I128" t="n">
-        <v>4.019865795767003</v>
+        <v>4.029421359665598</v>
       </c>
       <c r="J128" t="n">
         <v>4.42506930284718</v>
@@ -6546,7 +6546,7 @@
         <v>4.239508729583823</v>
       </c>
       <c r="I129" t="n">
-        <v>3.787224633687986</v>
+        <v>3.792642893850955</v>
       </c>
       <c r="J129" t="n">
         <v>4.404447137295326</v>
@@ -6593,7 +6593,7 @@
         <v>4.096586915556034</v>
       </c>
       <c r="I130" t="n">
-        <v>3.671417098073852</v>
+        <v>3.715399380495185</v>
       </c>
       <c r="J130" t="n">
         <v>4.389933141622743</v>
@@ -6640,7 +6640,7 @@
         <v>3.932681712314608</v>
       </c>
       <c r="I131" t="n">
-        <v>3.840120766909732</v>
+        <v>3.896028069838139</v>
       </c>
       <c r="J131" t="n">
         <v>4.442182763290342</v>
@@ -6687,7 +6687,7 @@
         <v>3.544069141434486</v>
       </c>
       <c r="I132" t="n">
-        <v>3.700241842410581</v>
+        <v>3.767699300161261</v>
       </c>
       <c r="J132" t="n">
         <v>4.3503783966924</v>
@@ -6734,7 +6734,7 @@
         <v>4.510975968235329</v>
       </c>
       <c r="I133" t="n">
-        <v>3.948818059514918</v>
+        <v>4.014532604793932</v>
       </c>
       <c r="J133" t="n">
         <v>4.445688185323541</v>
@@ -6781,7 +6781,7 @@
         <v>4.114970143314903</v>
       </c>
       <c r="I134" t="n">
-        <v>3.914739075685084</v>
+        <v>3.959008267315462</v>
       </c>
       <c r="J134" t="n">
         <v>4.316584023080848</v>
@@ -6828,7 +6828,7 @@
         <v>4.173744365852228</v>
       </c>
       <c r="I135" t="n">
-        <v>4.060848118069989</v>
+        <v>4.080725634682054</v>
       </c>
       <c r="J135" t="n">
         <v>4.327627163075682</v>
@@ -6875,7 +6875,7 @@
         <v>4.410434328313459</v>
       </c>
       <c r="I136" t="n">
-        <v>3.954717441537715</v>
+        <v>3.974111280737651</v>
       </c>
       <c r="J136" t="n">
         <v>4.424130420968813</v>
@@ -6922,7 +6922,7 @@
         <v>4.055240899034176</v>
       </c>
       <c r="I137" t="n">
-        <v>3.930986020085605</v>
+        <v>3.98769312124621</v>
       </c>
       <c r="J137" t="n">
         <v>4.4817229601536</v>
@@ -6969,7 +6969,7 @@
         <v>4.430698765015729</v>
       </c>
       <c r="I138" t="n">
-        <v>4.048381532061762</v>
+        <v>4.078516263020841</v>
       </c>
       <c r="J138" t="n">
         <v>4.45344356003945</v>
@@ -7016,7 +7016,7 @@
         <v>4.126056496519853</v>
       </c>
       <c r="I139" t="n">
-        <v>3.999485163535483</v>
+        <v>4.043303544188432</v>
       </c>
       <c r="J139" t="n">
         <v>4.399312874614113</v>
@@ -7063,7 +7063,7 @@
         <v>3.886653785285574</v>
       </c>
       <c r="I140" t="n">
-        <v>3.739676848341314</v>
+        <v>3.831212134440173</v>
       </c>
       <c r="J140" t="n">
         <v>4.339780033793477</v>
@@ -7110,7 +7110,7 @@
         <v>4.264308589518238</v>
       </c>
       <c r="I141" t="n">
-        <v>3.703243815020586</v>
+        <v>3.761381755542825</v>
       </c>
       <c r="J141" t="n">
         <v>4.398796231182566</v>
@@ -7157,7 +7157,7 @@
         <v>4.376748718974227</v>
       </c>
       <c r="I142" t="n">
-        <v>3.715848125700297</v>
+        <v>3.724322402785845</v>
       </c>
       <c r="J142" t="n">
         <v>4.381158972529247</v>
@@ -7204,7 +7204,7 @@
         <v>3.912791393178055</v>
       </c>
       <c r="I143" t="n">
-        <v>3.312022046297275</v>
+        <v>3.502861112196311</v>
       </c>
       <c r="J143" t="n">
         <v>4.418830333139771</v>
@@ -7251,7 +7251,7 @@
         <v>3.119750818497948</v>
       </c>
       <c r="I144" t="n">
-        <v>2.979470026916292</v>
+        <v>2.991542844515403</v>
       </c>
       <c r="J144" t="n">
         <v>3.834131082507926</v>
@@ -7298,7 +7298,7 @@
         <v>3.079435685495127</v>
       </c>
       <c r="I145" t="n">
-        <v>2.953041963787853</v>
+        <v>3.02861713134196</v>
       </c>
       <c r="J145" t="n">
         <v>3.806300965437248</v>
@@ -7345,7 +7345,7 @@
         <v>3.867416906132132</v>
       </c>
       <c r="I146" t="n">
-        <v>3.130514388850737</v>
+        <v>3.188661937470063</v>
       </c>
       <c r="J146" t="n">
         <v>3.915231662998421</v>
@@ -7439,7 +7439,7 @@
         <v>3.248716881703229</v>
       </c>
       <c r="I148" t="n">
-        <v>3.662776918222469</v>
+        <v>3.664269100957483</v>
       </c>
       <c r="J148" t="n">
         <v>4.279461911369749</v>
@@ -7486,7 +7486,7 @@
         <v>3.750047052571529</v>
       </c>
       <c r="I149" t="n">
-        <v>3.951836483785692</v>
+        <v>4.014527249610624</v>
       </c>
       <c r="J149" t="n">
         <v>4.227095723383543</v>
@@ -7533,7 +7533,7 @@
         <v>3.934333525303893</v>
       </c>
       <c r="I150" t="n">
-        <v>4.01547249594436</v>
+        <v>4.045075522505037</v>
       </c>
       <c r="J150" t="n">
         <v>4.327874607224911</v>
@@ -7580,7 +7580,7 @@
         <v>3.946147493344169</v>
       </c>
       <c r="I151" t="n">
-        <v>3.919415118833565</v>
+        <v>3.946187062575936</v>
       </c>
       <c r="J151" t="n">
         <v>4.342142065622167</v>
@@ -7627,7 +7627,7 @@
         <v>4.001955807036672</v>
       </c>
       <c r="I152" t="n">
-        <v>3.928839327555134</v>
+        <v>3.945527614808352</v>
       </c>
       <c r="J152" t="n">
         <v>4.090939453375814</v>
@@ -7674,7 +7674,7 @@
         <v>4.38858716035999</v>
       </c>
       <c r="I153" t="n">
-        <v>3.917370612763153</v>
+        <v>3.92921023389056</v>
       </c>
       <c r="J153" t="n">
         <v>4.300831613413836</v>
@@ -7721,7 +7721,7 @@
         <v>4.440968395490838</v>
       </c>
       <c r="I154" t="n">
-        <v>3.92288232809232</v>
+        <v>3.954670604813582</v>
       </c>
       <c r="J154" t="n">
         <v>4.371513751948691</v>
@@ -7768,7 +7768,7 @@
         <v>4.451552514325462</v>
       </c>
       <c r="I155" t="n">
-        <v>3.910914820907924</v>
+        <v>3.950935520346143</v>
       </c>
       <c r="J155" t="n">
         <v>3.78742522375926</v>
@@ -7815,7 +7815,7 @@
         <v>4.358675639587982</v>
       </c>
       <c r="I156" t="n">
-        <v>4.035083553621486</v>
+        <v>4.044762635508042</v>
       </c>
       <c r="J156" t="n">
         <v>4.036332350258601</v>
@@ -7862,7 +7862,7 @@
         <v>3.265546545441957</v>
       </c>
       <c r="I157" t="n">
-        <v>3.995767429296227</v>
+        <v>4.052139250722339</v>
       </c>
       <c r="J157" t="n">
         <v>3.811574118174234</v>
@@ -7909,7 +7909,7 @@
         <v>3.601213648163839</v>
       </c>
       <c r="I158" t="n">
-        <v>3.715074592171013</v>
+        <v>3.827719122579151</v>
       </c>
       <c r="J158" t="n">
         <v>4.333788100858255</v>
@@ -7956,7 +7956,7 @@
         <v>4.066533540234587</v>
       </c>
       <c r="I159" t="n">
-        <v>3.612296020188658</v>
+        <v>3.760749441647849</v>
       </c>
       <c r="J159" t="n">
         <v>4.351546994871983</v>
@@ -8003,7 +8003,7 @@
         <v>4.062176292886937</v>
       </c>
       <c r="I160" t="n">
-        <v>3.890523048380647</v>
+        <v>3.904585826781817</v>
       </c>
       <c r="J160" t="n">
         <v>4.497772660842161</v>
@@ -8050,7 +8050,7 @@
         <v>4.136164833398819</v>
       </c>
       <c r="I161" t="n">
-        <v>3.504498389102134</v>
+        <v>3.558857862012902</v>
       </c>
       <c r="J161" t="n">
         <v>3.922213314761063</v>
@@ -8097,7 +8097,7 @@
         <v>4.219793726911266</v>
       </c>
       <c r="I162" t="n">
-        <v>3.840378244658153</v>
+        <v>3.845749209804556</v>
       </c>
       <c r="J162" t="n">
         <v>3.16981398083833</v>
@@ -8144,7 +8144,7 @@
         <v>4.388837158381243</v>
       </c>
       <c r="I163" t="n">
-        <v>3.914858221431829</v>
+        <v>3.953946195974417</v>
       </c>
       <c r="J163" t="n">
         <v>3.175129775316977</v>
@@ -8191,7 +8191,7 @@
         <v>4.520572839453024</v>
       </c>
       <c r="I164" t="n">
-        <v>3.838651195247926</v>
+        <v>3.887837376425834</v>
       </c>
       <c r="J164" t="n">
         <v>4.200529639264271</v>
@@ -8238,7 +8238,7 @@
         <v>3.879258694856951</v>
       </c>
       <c r="I165" t="n">
-        <v>3.919152927862541</v>
+        <v>3.972699743846549</v>
       </c>
       <c r="J165" t="n">
         <v>4.320458438931437</v>
@@ -8285,7 +8285,7 @@
         <v>3.990738443164864</v>
       </c>
       <c r="I166" t="n">
-        <v>3.885086942838426</v>
+        <v>3.902593023520809</v>
       </c>
       <c r="J166" t="n">
         <v>4.307313619486566</v>
@@ -8332,7 +8332,7 @@
         <v>4.476998314888178</v>
       </c>
       <c r="I167" t="n">
-        <v>3.619451324969905</v>
+        <v>3.625148245569803</v>
       </c>
       <c r="J167" t="n">
         <v>4.105381994958631</v>
@@ -8379,7 +8379,7 @@
         <v>4.270565847932977</v>
       </c>
       <c r="I168" t="n">
-        <v>3.860827779683563</v>
+        <v>3.880265142954401</v>
       </c>
       <c r="J168" t="n">
         <v>4.024671741917327</v>
@@ -8426,7 +8426,7 @@
         <v>4.384514791445758</v>
       </c>
       <c r="I169" t="n">
-        <v>3.704167453330473</v>
+        <v>3.806982713902637</v>
       </c>
       <c r="J169" t="n">
         <v>3.82658394096151</v>
@@ -8473,7 +8473,7 @@
         <v>4.109688250699136</v>
       </c>
       <c r="I170" t="n">
-        <v>3.859617931776806</v>
+        <v>3.867091253594946</v>
       </c>
       <c r="J170" t="n">
         <v>4.314959810875572</v>
@@ -8520,7 +8520,7 @@
         <v>3.536815105466626</v>
       </c>
       <c r="I171" t="n">
-        <v>3.788820909359497</v>
+        <v>3.818709022973037</v>
       </c>
       <c r="J171" t="n">
         <v>4.018804939239799</v>
@@ -8567,7 +8567,7 @@
         <v>3.912982877515565</v>
       </c>
       <c r="I172" t="n">
-        <v>3.843963585714524</v>
+        <v>3.87985921642417</v>
       </c>
       <c r="J172" t="n">
         <v>4.376989664135332</v>
@@ -8614,7 +8614,7 @@
         <v>4.002911162298353</v>
       </c>
       <c r="I173" t="n">
-        <v>3.602398316836297</v>
+        <v>3.606450332039377</v>
       </c>
       <c r="J173" t="n">
         <v>4.313656437038965</v>
@@ -8661,7 +8661,7 @@
         <v>3.799560672254333</v>
       </c>
       <c r="I174" t="n">
-        <v>3.595244551046403</v>
+        <v>3.607064346317301</v>
       </c>
       <c r="J174" t="n">
         <v>4.278726762327061</v>
@@ -8708,7 +8708,7 @@
         <v>3.85438155817546</v>
       </c>
       <c r="I175" t="n">
-        <v>3.657728518795899</v>
+        <v>3.705360063417578</v>
       </c>
       <c r="J175" t="n">
         <v>3.952689476747813</v>
@@ -8755,7 +8755,7 @@
         <v>4.112399758851655</v>
       </c>
       <c r="I176" t="n">
-        <v>3.694666356669547</v>
+        <v>3.836446009639017</v>
       </c>
       <c r="J176" t="n">
         <v>4.272219351870405</v>
@@ -8802,7 +8802,7 @@
         <v>4.093189082330896</v>
       </c>
       <c r="I177" t="n">
-        <v>3.94877095752283</v>
+        <v>3.948928937290648</v>
       </c>
       <c r="J177" t="n">
         <v>4.37662878425415</v>
@@ -8849,7 +8849,7 @@
         <v>4.193629209572689</v>
       </c>
       <c r="I178" t="n">
-        <v>3.564161966011955</v>
+        <v>3.579556108671053</v>
       </c>
       <c r="J178" t="n">
         <v>4.365092874622189</v>
@@ -8896,7 +8896,7 @@
         <v>4.103445065839446</v>
       </c>
       <c r="I179" t="n">
-        <v>3.855331716169259</v>
+        <v>3.902902108101893</v>
       </c>
       <c r="J179" t="n">
         <v>4.368652865387152</v>
@@ -8943,7 +8943,7 @@
         <v>4.042245915347682</v>
       </c>
       <c r="I180" t="n">
-        <v>3.714160911540997</v>
+        <v>3.755780599885818</v>
       </c>
       <c r="J180" t="n">
         <v>4.365168943393602</v>
@@ -8990,7 +8990,7 @@
         <v>4.39294266712016</v>
       </c>
       <c r="I181" t="n">
-        <v>3.608441342150203</v>
+        <v>3.638321998374003</v>
       </c>
       <c r="J181" t="n">
         <v>4.330621933160208</v>
@@ -9037,7 +9037,7 @@
         <v>4.500452042341182</v>
       </c>
       <c r="I182" t="n">
-        <v>3.91579271617315</v>
+        <v>3.913552529046573</v>
       </c>
       <c r="J182" t="n">
         <v>4.435698315580076</v>
@@ -9084,7 +9084,7 @@
         <v>4.406658576608447</v>
       </c>
       <c r="I183" t="n">
-        <v>3.885919674167101</v>
+        <v>3.916876497188761</v>
       </c>
       <c r="J183" t="n">
         <v>4.305646129450444</v>
@@ -9131,7 +9131,7 @@
         <v>4.365530500047067</v>
       </c>
       <c r="I184" t="n">
-        <v>3.907856398024813</v>
+        <v>3.949486680611725</v>
       </c>
       <c r="J184" t="n">
         <v>4.006181688105888</v>
@@ -9178,7 +9178,7 @@
         <v>4.224372742444607</v>
       </c>
       <c r="I185" t="n">
-        <v>3.607863470756642</v>
+        <v>3.613794203592869</v>
       </c>
       <c r="J185" t="n">
         <v>4.351487723515666</v>
@@ -9225,7 +9225,7 @@
         <v>4.426121665367336</v>
       </c>
       <c r="I186" t="n">
-        <v>3.601925744005994</v>
+        <v>3.662680070392471</v>
       </c>
       <c r="J186" t="n">
         <v>4.401429681637602</v>
@@ -9272,7 +9272,7 @@
         <v>4.180594197783563</v>
       </c>
       <c r="I187" t="n">
-        <v>3.565828407915003</v>
+        <v>3.610142140947574</v>
       </c>
       <c r="J187" t="n">
         <v>4.30964018367008</v>
@@ -9319,7 +9319,7 @@
         <v>4.459308102648578</v>
       </c>
       <c r="I188" t="n">
-        <v>3.645719095263376</v>
+        <v>3.663563177084231</v>
       </c>
       <c r="J188" t="n">
         <v>4.158009596203534</v>
@@ -9366,7 +9366,7 @@
         <v>3.621485668632753</v>
       </c>
       <c r="I189" t="n">
-        <v>3.491804166054254</v>
+        <v>3.556297246658916</v>
       </c>
       <c r="J189" t="n">
         <v>4.118105160302176</v>
@@ -9413,7 +9413,7 @@
         <v>4.063157937894026</v>
       </c>
       <c r="I190" t="n">
-        <v>3.547447180198317</v>
+        <v>3.592147788158353</v>
       </c>
       <c r="J190" t="n">
         <v>4.249519158230891</v>
@@ -9460,7 +9460,7 @@
         <v>3.964465563443779</v>
       </c>
       <c r="I191" t="n">
-        <v>3.633783871784036</v>
+        <v>3.641494307696229</v>
       </c>
       <c r="J191" t="n">
         <v>4.350807071313607</v>
@@ -9507,7 +9507,7 @@
         <v>4.518836192980473</v>
       </c>
       <c r="I192" t="n">
-        <v>3.639264524302276</v>
+        <v>3.634322518530846</v>
       </c>
       <c r="J192" t="n">
         <v>4.463206153720268</v>
@@ -9554,7 +9554,7 @@
         <v>4.72795057823737</v>
       </c>
       <c r="I193" t="n">
-        <v>3.65497459628327</v>
+        <v>3.660639944501241</v>
       </c>
       <c r="J193" t="n">
         <v>4.426555157124133</v>
@@ -9601,7 +9601,7 @@
         <v>4.339585578408034</v>
       </c>
       <c r="I194" t="n">
-        <v>3.618918355464013</v>
+        <v>3.637685894191004</v>
       </c>
       <c r="J194" t="n">
         <v>4.245173686451366</v>
@@ -9648,7 +9648,7 @@
         <v>3.989652609539844</v>
       </c>
       <c r="I195" t="n">
-        <v>3.642130899344195</v>
+        <v>3.642235991502401</v>
       </c>
       <c r="J195" t="n">
         <v>4.20779613765541</v>
@@ -9695,7 +9695,7 @@
         <v>3.346633189409227</v>
       </c>
       <c r="I196" t="n">
-        <v>3.2339427364489</v>
+        <v>3.403551705025323</v>
       </c>
       <c r="J196" t="n">
         <v>4.342583673506122</v>
@@ -9742,7 +9742,7 @@
         <v>3.620633292592357</v>
       </c>
       <c r="I197" t="n">
-        <v>3.563684458327595</v>
+        <v>3.609450232475193</v>
       </c>
       <c r="J197" t="n">
         <v>4.165832632970229</v>
@@ -9789,7 +9789,7 @@
         <v>3.481668171952043</v>
       </c>
       <c r="I198" t="n">
-        <v>3.54921901801432</v>
+        <v>3.581361581201657</v>
       </c>
       <c r="J198" t="n">
         <v>3.393698435220752</v>
@@ -9836,7 +9836,7 @@
         <v>3.821094404910545</v>
       </c>
       <c r="I199" t="n">
-        <v>3.493943908294864</v>
+        <v>3.562523327894396</v>
       </c>
       <c r="J199" t="n">
         <v>3.706548437602892</v>
@@ -9883,7 +9883,7 @@
         <v>3.090128719835159</v>
       </c>
       <c r="I200" t="n">
-        <v>3.332264128094731</v>
+        <v>3.487234169618598</v>
       </c>
       <c r="J200" t="n">
         <v>4.127714509973634</v>
@@ -9930,7 +9930,7 @@
         <v>3.430592397468193</v>
       </c>
       <c r="I201" t="n">
-        <v>3.443415891582838</v>
+        <v>3.529573926991053</v>
       </c>
       <c r="J201" t="n">
         <v>3.231595892187739</v>
@@ -9977,7 +9977,7 @@
         <v>2.844382141200249</v>
       </c>
       <c r="I202" t="n">
-        <v>3.4245850963527</v>
+        <v>3.565840674965376</v>
       </c>
       <c r="J202" t="n">
         <v>2.95286071586917</v>
@@ -10024,7 +10024,7 @@
         <v>3.413462038960685</v>
       </c>
       <c r="I203" t="n">
-        <v>3.527263778104581</v>
+        <v>3.570977821731864</v>
       </c>
       <c r="J203" t="n">
         <v>2.954855438445589</v>
@@ -10071,7 +10071,7 @@
         <v>3.192685492322559</v>
       </c>
       <c r="I204" t="n">
-        <v>3.460582123570787</v>
+        <v>3.568867084945516</v>
       </c>
       <c r="J204" t="n">
         <v>3.161056160013565</v>
@@ -10118,7 +10118,7 @@
         <v>3.789890699252256</v>
       </c>
       <c r="I205" t="n">
-        <v>3.55547206431106</v>
+        <v>3.585206643600645</v>
       </c>
       <c r="J205" t="n">
         <v>3.533676994876731</v>
@@ -10165,7 +10165,7 @@
         <v>4.2300767470102</v>
       </c>
       <c r="I206" t="n">
-        <v>3.53600745858158</v>
+        <v>3.562602352801239</v>
       </c>
       <c r="J206" t="n">
         <v>3.838780182055726</v>
@@ -10212,7 +10212,7 @@
         <v>4.435096143532604</v>
       </c>
       <c r="I207" t="n">
-        <v>3.507253329863534</v>
+        <v>3.513298680328005</v>
       </c>
       <c r="J207" t="n">
         <v>4.023904844154146</v>
@@ -10259,7 +10259,7 @@
         <v>3.928818166010334</v>
       </c>
       <c r="I208" t="n">
-        <v>3.475210045241661</v>
+        <v>3.500146482243698</v>
       </c>
       <c r="J208" t="n">
         <v>3.775059213261614</v>
@@ -10306,7 +10306,7 @@
         <v>3.190960109155868</v>
       </c>
       <c r="I209" t="n">
-        <v>3.411064187815331</v>
+        <v>3.723703611744433</v>
       </c>
       <c r="J209" t="n">
         <v>3.935339358359093</v>
@@ -10353,7 +10353,7 @@
         <v>3.941372398004702</v>
       </c>
       <c r="I210" t="n">
-        <v>3.410469109879108</v>
+        <v>3.484032405146253</v>
       </c>
       <c r="J210" t="n">
         <v>3.262140974394219</v>
@@ -10400,7 +10400,7 @@
         <v>3.10964541056051</v>
       </c>
       <c r="I211" t="n">
-        <v>3.68890613820726</v>
+        <v>3.776493877621619</v>
       </c>
       <c r="J211" t="n">
         <v>3.373042064958538</v>
@@ -10447,7 +10447,7 @@
         <v>3.480321218500624</v>
       </c>
       <c r="I212" t="n">
-        <v>3.872018885470817</v>
+        <v>3.912536930749893</v>
       </c>
       <c r="J212" t="n">
         <v>3.200776208787797</v>
@@ -10494,7 +10494,7 @@
         <v>4.250044353264087</v>
       </c>
       <c r="I213" t="n">
-        <v>3.861819860407428</v>
+        <v>3.88125792228379</v>
       </c>
       <c r="J213" t="n">
         <v>3.927614061114158</v>
@@ -10541,7 +10541,7 @@
         <v>3.412766051051069</v>
       </c>
       <c r="I214" t="n">
-        <v>3.615194106174394</v>
+        <v>3.760414337224742</v>
       </c>
       <c r="J214" t="n">
         <v>4.063863903249756</v>
@@ -10588,7 +10588,7 @@
         <v>4.366395160554389</v>
       </c>
       <c r="I215" t="n">
-        <v>3.965490304943881</v>
+        <v>3.987795482823612</v>
       </c>
       <c r="J215" t="n">
         <v>3.201503770207961</v>
@@ -10635,7 +10635,7 @@
         <v>3.920812826290955</v>
       </c>
       <c r="I216" t="n">
-        <v>3.914414450954572</v>
+        <v>3.943097157400153</v>
       </c>
       <c r="J216" t="n">
         <v>3.157700471556718</v>
@@ -10682,7 +10682,7 @@
         <v>3.523960243038684</v>
       </c>
       <c r="I217" t="n">
-        <v>3.62660157686437</v>
+        <v>3.631299992442762</v>
       </c>
       <c r="J217" t="n">
         <v>3.82856815569939</v>
@@ -10729,7 +10729,7 @@
         <v>4.468639471821984</v>
       </c>
       <c r="I218" t="n">
-        <v>3.581012140365845</v>
+        <v>3.587363627855477</v>
       </c>
       <c r="J218" t="n">
         <v>4.331904855126635</v>
@@ -10776,7 +10776,7 @@
         <v>3.53566341783376</v>
       </c>
       <c r="I219" t="n">
-        <v>3.542663150463721</v>
+        <v>3.656964417170485</v>
       </c>
       <c r="J219" t="n">
         <v>3.956200657700599</v>
@@ -10823,7 +10823,7 @@
         <v>4.538060535495887</v>
       </c>
       <c r="I220" t="n">
-        <v>3.90741201086436</v>
+        <v>3.903103144083989</v>
       </c>
       <c r="J220" t="n">
         <v>4.374397413536679</v>
@@ -10870,7 +10870,7 @@
         <v>4.430654182371899</v>
       </c>
       <c r="I221" t="n">
-        <v>3.740301262733635</v>
+        <v>3.831099655240035</v>
       </c>
       <c r="J221" t="n">
         <v>4.410256108511714</v>
@@ -10917,7 +10917,7 @@
         <v>4.441655331135221</v>
       </c>
       <c r="I222" t="n">
-        <v>3.547572442702108</v>
+        <v>3.584659699319043</v>
       </c>
       <c r="J222" t="n">
         <v>4.36991494628356</v>
@@ -10964,7 +10964,7 @@
         <v>4.5056481435462</v>
       </c>
       <c r="I223" t="n">
-        <v>3.614371265455272</v>
+        <v>3.625129291304294</v>
       </c>
       <c r="J223" t="n">
         <v>4.352695018133104</v>
@@ -11011,7 +11011,7 @@
         <v>4.246298833914643</v>
       </c>
       <c r="I224" t="n">
-        <v>3.841773503765565</v>
+        <v>3.847661906875425</v>
       </c>
       <c r="J224" t="n">
         <v>3.720287684157606</v>
@@ -11058,7 +11058,7 @@
         <v>4.401975585206037</v>
       </c>
       <c r="I225" t="n">
-        <v>3.977802476845941</v>
+        <v>4.0082830595693</v>
       </c>
       <c r="J225" t="n">
         <v>4.08573979776811</v>
@@ -11105,7 +11105,7 @@
         <v>4.461870656095211</v>
       </c>
       <c r="I226" t="n">
-        <v>3.636887328076353</v>
+        <v>3.663974186297571</v>
       </c>
       <c r="J226" t="n">
         <v>3.0190501094747</v>
@@ -11152,7 +11152,7 @@
         <v>3.913578029097797</v>
       </c>
       <c r="I227" t="n">
-        <v>3.984989850567934</v>
+        <v>4.03442665359973</v>
       </c>
       <c r="J227" t="n">
         <v>3.84535971054933</v>
@@ -11199,7 +11199,7 @@
         <v>3.559795228152597</v>
       </c>
       <c r="I228" t="n">
-        <v>3.756421188543697</v>
+        <v>3.895282159016791</v>
       </c>
       <c r="J228" t="n">
         <v>3.680462722283683</v>
@@ -11246,7 +11246,7 @@
         <v>4.138759388028165</v>
       </c>
       <c r="I229" t="n">
-        <v>3.628194938144277</v>
+        <v>3.640469936449796</v>
       </c>
       <c r="J229" t="n">
         <v>3.40954903444975</v>
@@ -11293,7 +11293,7 @@
         <v>4.417576579444694</v>
       </c>
       <c r="I230" t="n">
-        <v>3.890026225481454</v>
+        <v>3.942865649635902</v>
       </c>
       <c r="J230" t="n">
         <v>4.104442284173867</v>
@@ -11340,7 +11340,7 @@
         <v>4.444260436196455</v>
       </c>
       <c r="I231" t="n">
-        <v>4.083026139511199</v>
+        <v>4.373134787799334</v>
       </c>
       <c r="J231" t="n">
         <v>4.256406227288949</v>
@@ -11387,7 +11387,7 @@
         <v>4.176596741471936</v>
       </c>
       <c r="I232" t="n">
-        <v>4.079474397797048</v>
+        <v>4.091464808196903</v>
       </c>
       <c r="J232" t="n">
         <v>4.431103474193792</v>
@@ -11434,7 +11434,7 @@
         <v>4.455257028185182</v>
       </c>
       <c r="I233" t="n">
-        <v>3.842944773148886</v>
+        <v>3.854452020779741</v>
       </c>
       <c r="J233" t="n">
         <v>4.348724960440675</v>
@@ -11481,7 +11481,7 @@
         <v>3.461204842313601</v>
       </c>
       <c r="I234" t="n">
-        <v>3.918882904371543</v>
+        <v>3.935319973251959</v>
       </c>
       <c r="J234" t="n">
         <v>4.284259221094626</v>
@@ -11528,7 +11528,7 @@
         <v>2.593303927193698</v>
       </c>
       <c r="I235" t="n">
-        <v>2.698256908755016</v>
+        <v>2.75309587287084</v>
       </c>
       <c r="J235" t="n">
         <v>3.015438785672434</v>
@@ -11575,7 +11575,7 @@
         <v>2.961077454391755</v>
       </c>
       <c r="I236" t="n">
-        <v>3.623628069571442</v>
+        <v>3.63589384900286</v>
       </c>
       <c r="J236" t="n">
         <v>4.371935607856287</v>
@@ -11622,7 +11622,7 @@
         <v>3.630498148705965</v>
       </c>
       <c r="I237" t="n">
-        <v>4.043989604131998</v>
+        <v>4.06898929619208</v>
       </c>
       <c r="J237" t="n">
         <v>4.051735086620281</v>
@@ -11669,7 +11669,7 @@
         <v>3.778561869025528</v>
       </c>
       <c r="I238" t="n">
-        <v>4.044003130103752</v>
+        <v>4.118543178809901</v>
       </c>
       <c r="J238" t="n">
         <v>3.700855614649301</v>
@@ -11716,7 +11716,7 @@
         <v>3.685594697603239</v>
       </c>
       <c r="I239" t="n">
-        <v>3.89725564415806</v>
+        <v>3.962732732710537</v>
       </c>
       <c r="J239" t="n">
         <v>4.265713938371027</v>
@@ -11763,7 +11763,7 @@
         <v>3.080040744669969</v>
       </c>
       <c r="I240" t="n">
-        <v>3.794339976958739</v>
+        <v>3.946302915949987</v>
       </c>
       <c r="J240" t="n">
         <v>4.342452749267181</v>
@@ -11810,7 +11810,7 @@
         <v>3.442649772497271</v>
       </c>
       <c r="I241" t="n">
-        <v>3.840754625194184</v>
+        <v>3.918234328543155</v>
       </c>
       <c r="J241" t="n">
         <v>3.884777866311719</v>
@@ -11857,7 +11857,7 @@
         <v>3.589180033987231</v>
       </c>
       <c r="I242" t="n">
-        <v>3.94414362122671</v>
+        <v>3.984693183044459</v>
       </c>
       <c r="J242" t="n">
         <v>4.346157573699593</v>
@@ -11904,7 +11904,7 @@
         <v>3.915793273240412</v>
       </c>
       <c r="I243" t="n">
-        <v>3.903110747403837</v>
+        <v>3.956017014967616</v>
       </c>
       <c r="J243" t="n">
         <v>4.304404705744819</v>
@@ -11951,7 +11951,7 @@
         <v>4.26327762580086</v>
       </c>
       <c r="I244" t="n">
-        <v>3.923637567926241</v>
+        <v>4.015592218483691</v>
       </c>
       <c r="J244" t="n">
         <v>3.975345640887755</v>
@@ -11998,7 +11998,7 @@
         <v>4.413389016063013</v>
       </c>
       <c r="I245" t="n">
-        <v>3.921211087952608</v>
+        <v>3.974816518268361</v>
       </c>
       <c r="J245" t="n">
         <v>4.256555624488749</v>
@@ -12045,7 +12045,7 @@
         <v>3.569049574082012</v>
       </c>
       <c r="I246" t="n">
-        <v>3.941297142766639</v>
+        <v>3.991367190395876</v>
       </c>
       <c r="J246" t="n">
         <v>4.447506670703332</v>
@@ -12092,7 +12092,7 @@
         <v>4.497513652705118</v>
       </c>
       <c r="I247" t="n">
-        <v>4.006064245414189</v>
+        <v>4.015110665711328</v>
       </c>
       <c r="J247" t="n">
         <v>2.923383672485703</v>
@@ -12139,7 +12139,7 @@
         <v>4.056450389415605</v>
       </c>
       <c r="I248" t="n">
-        <v>3.909080807181122</v>
+        <v>3.939778095438198</v>
       </c>
       <c r="J248" t="n">
         <v>3.852039274938783</v>
@@ -12186,7 +12186,7 @@
         <v>3.829467144813664</v>
       </c>
       <c r="I249" t="n">
-        <v>3.747681241177863</v>
+        <v>3.818850335596188</v>
       </c>
       <c r="J249" t="n">
         <v>3.337717066064588</v>
@@ -12233,7 +12233,7 @@
         <v>4.361882765428244</v>
       </c>
       <c r="I250" t="n">
-        <v>3.528231609236872</v>
+        <v>3.539241894053266</v>
       </c>
       <c r="J250" t="n">
         <v>3.890498123901023</v>
@@ -12280,7 +12280,7 @@
         <v>4.17588267483983</v>
       </c>
       <c r="I251" t="n">
-        <v>3.683886053889738</v>
+        <v>3.6983225994965</v>
       </c>
       <c r="J251" t="n">
         <v>4.382285467174681</v>
@@ -12327,7 +12327,7 @@
         <v>4.305884765894001</v>
       </c>
       <c r="I252" t="n">
-        <v>3.50368724152885</v>
+        <v>3.5266697168557</v>
       </c>
       <c r="J252" t="n">
         <v>4.188213487531339</v>
@@ -12374,7 +12374,7 @@
         <v>4.410628002004968</v>
       </c>
       <c r="I253" t="n">
-        <v>3.478448087991328</v>
+        <v>3.517961170655336</v>
       </c>
       <c r="J253" t="n">
         <v>3.956248422717103</v>
@@ -12421,7 +12421,7 @@
         <v>3.858923400651792</v>
       </c>
       <c r="I254" t="n">
-        <v>3.454089059437146</v>
+        <v>3.574809133428452</v>
       </c>
       <c r="J254" t="n">
         <v>4.145256547660615</v>
@@ -12468,7 +12468,7 @@
         <v>4.372117665708307</v>
       </c>
       <c r="I255" t="n">
-        <v>3.570444649746564</v>
+        <v>3.589912125225295</v>
       </c>
       <c r="J255" t="n">
         <v>4.390483806071067</v>
@@ -12515,7 +12515,7 @@
         <v>3.783943751568123</v>
       </c>
       <c r="I256" t="n">
-        <v>3.596245951277685</v>
+        <v>3.624196394202801</v>
       </c>
       <c r="J256" t="n">
         <v>4.36420434015308</v>
@@ -12562,7 +12562,7 @@
         <v>4.449287882172738</v>
       </c>
       <c r="I257" t="n">
-        <v>3.753604085809065</v>
+        <v>3.814233816326207</v>
       </c>
       <c r="J257" t="n">
         <v>3.901936600089622</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig7_daily_timeseries_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig7_daily_timeseries_data.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
